--- a/scripts/scrum/importScrumModule.xlsx
+++ b/scripts/scrum/importScrumModule.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="14.25"/>
   <cols>
     <col width="17" customWidth="1" style="17" min="1" max="6"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>为用户提供安全可靠的账号体系与资料管理能力，支撑全平台身份识别。关联服务：User Service、Gateway。</t>
+          <t>为用户提供安全可靠的账号体系与资料管理能力，支撑全平台身份识别</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>覆盖活动从创建、审核、发现、报名、签到到总结的完整闭环，是平台核心业务。关联服务：Activity Service、AI Service。</t>
+          <t>覆盖活动从创建、审核、发现、报名、签到到总结评价的完整闭环，是平台核心业务</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>构建平台社交关系网络与兴趣社群，增强用户粘性与活动传播。关联服务：Social Service。</t>
+          <t>构建平台社交关系网络与兴趣社群，增强用户粘性与活动传播</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>为好友和小队成员提供实时沟通能力，支撑活动协调与社群运营。关联服务：IM Service。</t>
+          <t>为好友和小队成员提供实时沟通能力，支撑活动协调与社群运营</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EPIC-05 AI智能能力</t>
+          <t>EPIC-05 AI 智能能力</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>以AI提升内容审核效率、降低活动策划门槛、优化素材整理体验。关联服务：AI Service。</t>
+          <t>以 AI 提升内容审核效率、降低活动策划门槛、优化素材整理体验</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>为平台管理员提供统一的运营治理工具，保障平台内容安全与用户秩序。关联服务：Admin Service。</t>
+          <t>为平台管理员提供统一的运营治理工具，保障平台内容安全与用户秩序</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>将关键业务事件及时触达用户，提升响应效率与用户体验。</t>
+          <t>将关键业务事件及时触达用户，提升响应效率与用户体验</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>迭代0-基础设施</t>
+          <t>迭代0-启动与规划</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>为各业务服务提供统一入口、安全管控与服务间通信规范，支撑团队并行开发。关联服务：Gateway。</t>
+          <t>为各业务服务提供统一入口、安全管控与服务间通信规范，支撑团队并行开发</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>US-U-001 用户注册</t>
+          <t>US-U-001 使用邮箱、密码和唯一昵称注册个人账号</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1409,13 +1409,16 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>作为 访客
-我想要 使用邮箱和密码注册账号
-以便于 成为平台用户并开始使用 OnlyFriends 的各项功能</t>
+我想要 使用邮箱、密码和唯一昵称注册个人账号
+以便于 成为平台用户并开始使用活动浏览、报名和发起功能
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>US-U-001</t>
+          <t>US-U-001 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1425,12 +1428,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1447,7 +1450,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>US-U-002 邮箱激活</t>
+          <t>US-U-002 通过邮件激活链接或实践环境中的模拟激活方式完成账号激活</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1458,7 +1461,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1484,13 +1487,16 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>作为 新注册用户
-我想要 通过邮件中的激活链接完成账号激活
-以便于 验证邮箱有效性并正常使用平台功能</t>
+我想要 通过邮件激活链接或实践环境中的模拟激活方式完成账号激活
+以便于 验证邮箱有效性并正常登录平台
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>US-U-002</t>
+          <t>US-U-002 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1500,12 +1506,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1522,7 +1528,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US-U-003 用户登录</t>
+          <t>US-U-003 使用邮箱和密码登录并获取访问令牌</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1533,7 +1539,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1560,12 +1566,15 @@
         <is>
           <t>作为 已注册用户
 我想要 使用邮箱和密码登录并获取访问令牌
-以便于 访问需要身份认证的接口与页面</t>
+以便于 访问需要身份认证的接口与页面
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>US-U-003</t>
+          <t>US-U-003 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1575,12 +1584,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1597,7 +1606,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>US-U-004 令牌自动刷新</t>
+          <t>US-U-004 在 Access Token 过期时自动刷新令牌</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1608,7 +1617,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1635,12 +1644,15 @@
         <is>
           <t>作为 已登录用户
 我想要 在 Access Token 过期时自动刷新令牌
-以便于 保持登录状态而无需频繁重新输入账号密码</t>
+以便于 保持登录状态而无需频繁重新输入账号密码
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>US-U-004</t>
+          <t>US-U-004 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1650,12 +1662,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1672,7 +1684,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>US-U-005 编辑个人资料</t>
+          <t>US-U-005 编辑昵称、头像、性别、生日、个性签名和兴趣标签</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1683,7 +1695,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1710,12 +1722,15 @@
         <is>
           <t>作为 个人用户
 我想要 编辑昵称、头像、性别、生日、个性签名和兴趣标签
-以便于 完善个人形象并提升活动与社群的匹配度</t>
+以便于 完善个人形象并提升活动与社群匹配度
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>US-U-005</t>
+          <t>US-U-005 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1725,12 +1740,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1747,7 +1762,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>US-U-006 查看他人公开资料</t>
+          <t>US-U-006 查看其他用户的公开资料</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1758,7 +1773,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1785,12 +1800,15 @@
         <is>
           <t>作为 个人用户
 我想要 查看其他用户的公开资料
-以便于 决定是否关注对方或发起好友申请</t>
+以便于 决定是否关注对方或发起好友申请
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>US-U-006</t>
+          <t>US-U-006 P1 实践后延期</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1800,12 +1818,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1822,7 +1840,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>US-U-007 提交商家申请</t>
+          <t>US-U-007 提交商家申请并上传营业执照或营业凭证</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1833,7 +1851,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1859,13 +1877,16 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 提交商家申请并上传营业执照等资质凭证
-以便于 获得商家身份并发起商业类活动</t>
+我想要 提交商家申请并上传营业执照或营业凭证
+以便于 获得商家身份并发起商业类活动
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>US-U-007</t>
+          <t>US-U-007 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1875,12 +1896,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1897,7 +1918,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>US-U-008 查询商家申请状态</t>
+          <t>US-U-008 查询商家申请的审核进度、审核结果和驳回原因</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1908,7 +1929,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1934,13 +1955,16 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>作为 商家申请用户
-我想要 查询商家申请的审核进度与结果
-以便于 了解审核状态并在被驳回时及时补充材料</t>
+我想要 查询商家申请的审核进度、审核结果和驳回原因
+以便于 了解申请状态并及时补充材料
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>US-U-008</t>
+          <t>US-U-008 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1950,12 +1974,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1972,33 +1996,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>US-A-001 创建活动草稿</t>
+          <t>US-U-009 维护商家名称、商家昵称和关注活动领域</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>20009</v>
       </c>
       <c r="D18" t="n">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OnlyFriends/活动服务</t>
+          <t>OnlyFriends/用户服务</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2008,14 +2032,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>作为 活动发起人
-我想要 手动填写活动信息并保存为草稿
-以便于 在正式提交审核前反复修改和完善活动内容</t>
+          <t>作为 商家用户
+我想要 维护商家名称、商家昵称和关注活动领域
+以便于 向用户展示可信的商家身份和服务方向
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>US-A-001</t>
+          <t>US-U-009 P1 实践后延期</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2025,17 +2052,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -2047,220 +2074,229 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>US-A-002 提交活动审核</t>
+          <t>US-U-010 在活动详情或商家主页查看商家公开资料</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>20010</v>
       </c>
       <c r="D19" t="n">
+        <v>10001</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>迭代4-后续增强</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OnlyFriends/用户服务</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>作为 个人用户
+我想要 在活动详情或商家主页查看商家公开资料
+以便于 判断商家活动的可信度和适配度
+优先级：P2
+目标版本：v1.1
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>US-U-010 P2 实践后延期</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>US-A-001 填写活动名称、标签、简介、时间、地点、人数上限和报名截止时间并保存为草稿</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20011</v>
+      </c>
+      <c r="D20" t="n">
         <v>10002</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>迭代1-MVP核心链路</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>OnlyFriends/活动服务</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>关键</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>作为 活动发起人
+我想要 填写活动名称、标签、简介、时间、地点、人数上限和报名截止时间并保存为草稿
+以便于 在正式提交审核前完善活动内容
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>US-A-001 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>US-A-002 将草稿活动提交平台审核</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20012</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>OnlyFriends/活动服务</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>关键</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>作为 活动发起人
 我想要 将草稿活动提交平台审核
-以便于 活动通过审核后对外发布并开放报名</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>US-A-002</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+以便于 活动通过审核后对外发布并开放报名
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>US-A-002 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>US-A-003 接收审核结果通知</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>20011</v>
-      </c>
-      <c r="D20" t="n">
-        <v>10002</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>迭代1-MVP核心链路</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>OnlyFriends/活动服务</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>关键</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>作为 活动发起人
-我想要 收到活动审核结果通知（通过/驳回/要求修改）
-以便于 根据审核意见及时调整活动信息并重新提交</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>US-A-003</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>US-A-004 AI生成活动策划</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>20012</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10002</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>OnlyFriends/活动服务</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>作为 活动发起人
-我想要 输入活动主题后由 AI 自动生成活动策划草稿
-以便于 降低活动创建门槛并提高策划效率</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>US-A-004</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2308,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>US-A-005 模板创建与活动克隆</t>
+          <t>US-A-003 收到活动审核结果通知或页面提示（通过/驳回/要求修改）</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2283,7 +2319,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2293,12 +2329,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2309,13 +2345,16 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>作为 活动发起人
-我想要 从活动模板快速创建或克隆历史活动
-以便于 复用成功经验并减少重复填写工作</t>
+我想要 收到活动审核结果通知或页面提示（通过/驳回/要求修改）
+以便于 根据审核意见及时调整活动信息并重新提交
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>US-A-005</t>
+          <t>US-A-003 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2325,17 +2364,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2386,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>US-A-006 浏览活动列表</t>
+          <t>US-A-004 输入活动主题或选择活动类型后由 AI 自动生成活动策划草稿</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2358,7 +2397,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2368,12 +2407,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2383,14 +2422,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>作为 访客或个人用户
-我想要 在首页按推荐、最新等维度浏览活动列表
-以便于 快速发现感兴趣的活动</t>
+          <t>作为 活动发起人
+我想要 输入活动主题或选择活动类型后由 AI 自动生成活动策划草稿
+以便于 降低活动创建门槛并提高策划效率
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>US-A-006</t>
+          <t>US-A-004 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2400,17 +2442,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2464,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>US-A-007 附近活动与地图浏览</t>
+          <t>US-A-005 从常用模板快速创建活动或克隆历史活动</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2433,7 +2475,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2458,14 +2500,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>作为 个人用户
-我想要 基于当前定位查看附近活动并在地图模式中浏览
-以便于 便捷参与线下同城活动</t>
+          <t>作为 活动发起人
+我想要 从常用模板快速创建活动或克隆历史活动
+以便于 复用成功经验并减少重复填写工作
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>US-A-007</t>
+          <t>US-A-005 P1 实践后延期</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2475,12 +2520,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2497,7 +2542,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>US-A-008 筛选与搜索活动</t>
+          <t>US-A-006 在首页按推荐、最新、附近等维度浏览活动列表</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2508,7 +2553,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2518,12 +2563,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2533,14 +2578,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>作为 个人用户
-我想要 通过关键词和标签筛选活动
-以便于 精准找到符合个人兴趣的活动</t>
+          <t>作为 访客或个人用户
+我想要 在首页按推荐、最新、附近等维度浏览活动列表
+以便于 快速发现感兴趣的活动
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>US-A-008</t>
+          <t>US-A-006 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2550,17 +2598,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2620,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>US-A-009 查看活动详情</t>
+          <t>US-A-007 基于当前位置查看附近活动并在地图模式中浏览活动点位</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2583,7 +2631,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2593,12 +2641,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2609,13 +2657,16 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 查看活动的完整详情（时间、地点、名额、发起人、评价等）
-以便于 充分了解活动信息后做出是否报名的决策</t>
+我想要 基于当前位置查看附近活动并在地图模式中浏览活动点位
+以便于 便捷发现线下同城活动
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代必做</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>US-A-009</t>
+          <t>US-A-007 P1 第二次迭代必做</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2625,17 +2676,17 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2698,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US-A-010 报名活动</t>
+          <t>US-A-008 通过关键词、活动类型、时间范围、城市、费用和距离范围筛选活动</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2658,7 +2709,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2668,12 +2719,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2684,13 +2735,16 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 在名额充足时报名活动并填写附加信息
-以便于 确认参与活动并纳入活动组织方的参与者名单</t>
+我想要 通过关键词、活动类型、时间范围、城市、费用和距离范围筛选活动
+以便于 精准找到符合个人条件的活动
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>US-A-010</t>
+          <t>US-A-008 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2700,17 +2754,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2776,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US-A-011 加入等待队列</t>
+          <t>US-A-009 查看活动完整详情，包括时间、地点、名额、状态、发起人和报名要求</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2733,7 +2787,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2743,12 +2797,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2759,13 +2813,16 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 在活动名额已满时加入等待队列
-以便于 在有人取消报名时获得递补参与的机会</t>
+我想要 查看活动完整详情，包括时间、地点、名额、状态、发起人和报名要求
+以便于 充分了解活动信息后决定是否报名
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>US-A-011</t>
+          <t>US-A-009 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2775,17 +2832,17 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2854,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US-A-012 等待队列递补确认</t>
+          <t>US-A-010 在名额充足且满足信誉、年龄等报名条件时报名活动</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2808,7 +2865,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代1-首次迭代MVP</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2818,12 +2875,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2833,14 +2890,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>作为 等待队列中的用户
-我想要 在获得递补名额时收到通知并在规定时间内确认
-以便于 公平、及时地获得活动参与资格</t>
+          <t>作为 个人用户
+我想要 在名额充足且满足信誉、年龄等报名条件时报名活动
+以便于 确认参与活动并进入参与者名单
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>US-A-012</t>
+          <t>US-A-010 P0 第一次迭代必做</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2850,17 +2910,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v0.1</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2932,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US-A-013 取消报名</t>
+          <t>US-A-011 在活动名额已满时加入等待队列并查看当前等待人数</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2883,7 +2943,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2907,165 +2967,174 @@
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>作为 个人用户
+我想要 在活动名额已满时加入等待队列并查看当前等待人数
+以便于 在有人取消报名时获得递补机会
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>US-A-011 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>US-A-012 在获得递补名额时收到通知并在限定时间内确认</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20022</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>OnlyFriends/活动服务</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>作为 等待队列中的用户
+我想要 在获得递补名额时收到通知并在限定时间内确认
+以便于 公平、及时地获得活动参与资格
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>US-A-012 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>US-A-013 在报名截止前取消报名</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20023</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>OnlyFriends/活动服务</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>作为 已报名用户
 我想要 在报名截止前取消报名
-以便于 释放名额让其他用户参与</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>US-A-013</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>US-A-014 查看报名列表</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>20022</v>
-      </c>
-      <c r="D31" t="n">
-        <v>10002</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>OnlyFriends/活动服务</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>作为 活动发起人
-我想要 查看活动的报名用户列表
-以便于 掌握参与人数和参与者信息并做好活动组织准备</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>US-A-014</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>US-A-015 生成签到二维码</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>20023</v>
-      </c>
-      <c r="D32" t="n">
-        <v>10002</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>OnlyFriends/活动服务</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>作为 活动发起人
-我想要 生成带安全签名的签到二维码
-以便于 参与者在活动现场扫码完成签到</t>
+以便于 释放名额让其他用户参与
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>US-A-015</t>
+          <t>US-A-013 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3075,12 +3144,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3097,7 +3166,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US-A-016 扫码签到</t>
+          <t>US-A-014 查看活动报名用户列表和签到状态</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3108,7 +3177,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3133,14 +3202,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>作为 活动参与者
-我想要 扫描签到二维码完成到场签到（支持位置校验）
-以便于 记录实际参与情况并维护个人信誉分</t>
+          <t>作为 活动发起人
+我想要 查看活动报名用户列表和签到状态
+以便于 掌握参与人数、到场情况并做好组织准备
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>US-A-016</t>
+          <t>US-A-014 P1 第二次迭代择优</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3150,12 +3222,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3172,7 +3244,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>US-A-017 发布活动总结</t>
+          <t>US-A-015 在活动开始前生成带安全签名的签到二维码</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3183,7 +3255,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3209,13 +3281,16 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>作为 活动发起人
-我想要 在活动结束后发布图文总结（含 AI 图片分类辅助）
-以便于 沉淀活动成果并为后续活动提供参考素材</t>
+我想要 在活动开始前生成带安全签名的签到二维码
+以便于 参与者到场后扫码完成签到
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>US-A-017</t>
+          <t>US-A-015 P1 实践后延期</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3225,12 +3300,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3247,7 +3322,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>US-A-018 发表活动评价</t>
+          <t>US-A-016 扫描签到二维码并可选进行位置校验</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3258,7 +3333,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3284,13 +3359,16 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>作为 活动参与者
-我想要 对已结束的活动发表评价
-以便于 反馈参与体验并帮助其他用户做出参与决策</t>
+我想要 扫描签到二维码并可选进行位置校验
+以便于 记录真实到场情况并维护个人信誉
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>US-A-018</t>
+          <t>US-A-016 P1 实践后延期</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3300,12 +3378,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3322,23 +3400,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US-S-001 关注与粉丝管理</t>
+          <t>US-A-017 在活动结束后发布图文总结并确认 AI 图片分类结果</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>20027</v>
       </c>
       <c r="D36" t="n">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OnlyFriends/社群服务</t>
+          <t>OnlyFriends/活动服务</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3358,14 +3436,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>作为 个人用户
-我想要 关注其他用户并查看我的关注列表与粉丝列表
-以便于 建立单向社交关系并了解互动对象</t>
+          <t>作为 活动发起人
+我想要 在活动结束后发布图文总结并确认 AI 图片分类结果
+以便于 沉淀活动成果并整理活动素材
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>US-S-001</t>
+          <t>US-A-017 P1 实践后延期</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3375,12 +3456,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3397,23 +3478,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US-S-002 好友申请与管理</t>
+          <t>US-A-018 在活动结束后限定时间内发表评价</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>20028</v>
       </c>
       <c r="D37" t="n">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OnlyFriends/社群服务</t>
+          <t>OnlyFriends/活动服务</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3433,14 +3514,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>作为 个人用户
-我想要 向其他用户发起好友申请并在对方同意后成为好友
-以便于 进行私聊等更深度的社交互动</t>
+          <t>作为 活动参与者
+我想要 在活动结束后限定时间内发表评价
+以便于 反馈参与体验并帮助其他用户判断活动质量
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>US-S-002</t>
+          <t>US-A-018 P1 实践后延期</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3450,12 +3534,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3472,895 +3556,931 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US-S-003 好友备注与分组</t>
+          <t>US-A-019 创建活动时通过地图选点保存活动地点和坐标</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>20029</v>
       </c>
       <c r="D38" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>OnlyFriends/活动服务</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>作为 活动发起人
+我想要 创建活动时通过地图选点保存活动地点和坐标
+以便于 用户能够在附近活动和地图模式中准确查看位置
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代必做</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>US-A-019 P1 第二次迭代必做</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>US-A-020 在报名前看到确认窗口、安全须知摘要和必要报名信息填写项</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>20030</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10002</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>OnlyFriends/活动服务</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>关键</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>作为 报名用户
+我想要 在报名前看到确认窗口、安全须知摘要和必要报名信息填写项
+以便于 明确活动风险并提交完整报名信息
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>US-A-020 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>US-S-001 关注其他用户并查看关注列表与粉丝列表</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>20031</v>
+      </c>
+      <c r="D40" t="n">
         <v>10003</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>作为 个人用户
+我想要 关注其他用户并查看关注列表与粉丝列表
+以便于 建立单向社交关系并了解互动对象
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>US-S-001 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>US-S-002 通过个人主页、活动参与者列表或个人二维码发起好友申请</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>20032</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10003</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>OnlyFriends/社群服务</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>作为 个人用户
+我想要 通过个人主页、活动参与者列表或个人二维码发起好友申请
+以便于 与感兴趣的人建立好友关系
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>US-S-002 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>US-S-003 为好友设置备注和分组标签</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>20033</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10003</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>OnlyFriends/社群服务</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>作为 个人用户
 我想要 为好友设置备注和分组标签
-以便于 高效管理和识别社交关系</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>US-S-003</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
+以便于 高效管理和识别社交关系
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>US-S-003 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>US-S-004 创建兴趣小队</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>20030</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>US-S-004 创建兴趣小队并设置名称、标签、加入方式和人数上限</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>20034</v>
+      </c>
+      <c r="D43" t="n">
         <v>10003</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>作为 个人用户
 我想要 创建兴趣小队并设置名称、标签、加入方式和人数上限
-以便于 聚集志同道合的用户形成稳定社群</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>US-S-004</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+以便于 聚集志同道合的用户形成稳定社群
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>US-S-004 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>US-S-005 发现兴趣小队</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>20031</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>US-S-005 按照小队名称或标签搜索和浏览公开小队</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>20035</v>
+      </c>
+      <c r="D44" t="n">
         <v>10003</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 搜索和浏览公开的兴趣小队
-以便于 找到符合个人兴趣的社群并申请加入</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>US-S-005</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
+我想要 按照小队名称或标签搜索和浏览公开小队
+以便于 找到符合个人兴趣的社群
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>US-S-005 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>US-S-006 加入兴趣小队</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>20032</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>US-S-006 按小队规则直接加入或提交加入申请</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>20036</v>
+      </c>
+      <c r="D45" t="n">
         <v>10003</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>作为 个人用户
 我想要 按小队规则直接加入或提交加入申请
-以便于 成为小队成员并参与队内活动与互动</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>US-S-006</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+以便于 成为小队成员并参与队内活动与互动
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>US-S-006 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>US-S-007 审核小队加入申请</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>20033</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>US-S-007 审核用户的加入申请并决定同意或拒绝</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>20037</v>
+      </c>
+      <c r="D46" t="n">
         <v>10003</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>作为 小队队长或管理员
 我想要 审核用户的加入申请并决定同意或拒绝
-以便于 控制小队成员质量与社群氛围</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>US-S-007</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+以便于 控制小队成员质量与社群氛围
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>US-S-007 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>US-S-008 小队生命周期管理</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>20034</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>US-S-008 任命管理员、调整成员角色或解散小队</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>20038</v>
+      </c>
+      <c r="D47" t="n">
         <v>10003</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>作为 小队队长
 我想要 任命管理员、调整成员角色或解散小队
-以便于 有效管理小队的组织结构和生命周期</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>US-S-008</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+以便于 有效管理小队组织结构和生命周期
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>US-S-008 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>US-S-009 小队内协作互动</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>20035</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>US-S-009 发布队内活动并允许小队成员查看和报名</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>20039</v>
+      </c>
+      <c r="D48" t="n">
         <v>10003</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>作为 小队成员
-我想要 在小队内发布活动、查看积分榜、上传相册和文件、参与投票
-以便于 增强队内凝聚力并促进成员间的持续互动</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>US-S-009</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>作为 小队队长或管理员
+我想要 发布队内活动并允许小队成员查看和报名
+以便于 围绕兴趣小队组织稳定活动
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>US-S-009 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>US-S-010 小队积分激励</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>20036</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>US-S-010 通过参与活动、发布动态等行为获得积分并在积分榜展示</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>20040</v>
+      </c>
+      <c r="D49" t="n">
         <v>10003</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>迭代3-体验增强</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>迭代4-后续增强</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>OnlyFriends/社群服务</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>作为 小队成员
 我想要 通过参与活动、发布动态等行为获得积分并在积分榜展示
-以便于 获得成就感并激励持续参与队内活动</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>US-S-010</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+以便于 获得成就感并激励持续参与
+优先级：P2
+目标版本：v1.1
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>US-S-010 P2 实践后延期</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>OnlyFriends_v1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>US-I-001 好友私聊</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>20037</v>
-      </c>
-      <c r="D46" t="n">
-        <v>10004</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>OnlyFriends/即时通讯</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>作为 互为好友的用户
-我想要 与好友进行实时私聊
-以便于 在活动前后便捷沟通协调</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>US-I-001</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>US-I-002 小队群聊</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>20038</v>
-      </c>
-      <c r="D47" t="n">
-        <v>10004</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>OnlyFriends/即时通讯</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>作为 小队成员
-我想要 在小队群聊中收发消息
-以便于 及时同步队内信息和活动安排</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>US-I-002</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>US-I-003 会话列表与未读提醒</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>20039</v>
-      </c>
-      <c r="D48" t="n">
-        <v>10004</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>OnlyFriends/即时通讯</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>作为 IM用户
-我想要 查看会话列表及每个会话的未读消息数
-以便于 快速定位需要回复的对话</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>US-I-003</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>story</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>US-I-004 离线消息同步</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>20040</v>
-      </c>
-      <c r="D49" t="n">
-        <v>10004</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>OnlyFriends/即时通讯</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>作为 IM用户
-我想要 在离线后重新上线时拉取历史消息与未读消息
-以便于 不遗漏任何重要信息</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>US-I-004</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4372,33 +4492,33 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>US-I-005 撤回消息</t>
+          <t>US-S-011 发布群公告并在群聊中 @成员 或 @所有人</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>20041</v>
       </c>
       <c r="D50" t="n">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>迭代3-体验增强</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OnlyFriends/即时通讯</t>
+          <t>OnlyFriends/社群服务</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4408,14 +4528,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>作为 消息发送者
-我想要 在发送后 2 分钟内撤回已发送的消息
-以便于 及时纠正误发内容</t>
+          <t>作为 小队队长或管理员
+我想要 发布群公告并在群聊中 @成员 或 @所有人
+以便于 及时传达重要通知
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>US-I-005</t>
+          <t>US-S-011 P1 实践后延期</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4425,17 +4548,17 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>OnlyFriends_v1.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4447,33 +4570,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US-I-006 转发消息</t>
+          <t>US-S-012 发起或参与群投票</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>20042</v>
       </c>
       <c r="D51" t="n">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>迭代3-体验增强</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OnlyFriends/即时通讯</t>
+          <t>OnlyFriends/社群服务</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4483,14 +4606,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>作为 IM用户
-我想要 将消息转发给其他会话
-以便于 高效传递信息而无需重复输入</t>
+          <t>作为 小队成员
+我想要 发起或参与群投票
+以便于 共同决定活动时间、地点或队内事务
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>US-I-006</t>
+          <t>US-S-012 P1 实践后延期</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4500,17 +4626,17 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>OnlyFriends_v1.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4522,33 +4648,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US-AI-001 活动内容安全审核</t>
+          <t>US-S-013 上传和查看群文件</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>20043</v>
       </c>
       <c r="D52" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OnlyFriends/AI服务</t>
+          <t>OnlyFriends/社群服务</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4558,14 +4684,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>作为 平台运营方
-我想要 对用户提交的活动内容执行三层安全审核（规则引擎 + LLM + 人工兜底）
-以便于 在审核效率与内容合规性之间取得平衡</t>
+          <t>作为 小队成员
+我想要 上传和查看群文件
+以便于 共享活动资料和队内文档
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>US-AI-001</t>
+          <t>US-S-013 P1 实践后延期</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4575,17 +4704,17 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4597,23 +4726,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US-AI-002 AI活动策划生成</t>
+          <t>US-S-014 上传小队相册照片，队长和管理员可以删除不合适内容</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>20044</v>
       </c>
       <c r="D53" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OnlyFriends/AI服务</t>
+          <t>OnlyFriends/社群服务</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4633,14 +4762,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>作为 活动发起人
-我想要 输入主题后获得 AI 生成的完整活动策划方案（支持流式输出）
-以便于 快速完成活动设计并减少策划时间</t>
+          <t>作为 小队成员
+我想要 上传小队相册照片，队长和管理员可以删除不合适内容
+以便于 沉淀小队活动记忆并维护内容质量
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>US-AI-002</t>
+          <t>US-S-014 P1 实践后延期</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4650,12 +4782,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4672,23 +4804,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US-AI-003 活动图片智能分类</t>
+          <t>US-S-015 查看小队积分榜中的昵称、积分和名次</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>20045</v>
       </c>
       <c r="D54" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OnlyFriends/AI服务</t>
+          <t>OnlyFriends/社群服务</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4708,14 +4840,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>作为 活动发起人
-我想要 在发布活动总结时由 AI 自动对图片进行分类
-以便于 高效整理活动素材并提升总结内容的可读性</t>
+          <t>作为 小队成员
+我想要 查看小队积分榜中的昵称、积分和名次
+以便于 了解自己在小队中的活跃度排名
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>US-AI-003</t>
+          <t>US-S-015 P1 实践后延期</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4725,12 +4860,12 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4747,33 +4882,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>US-ADM-001 管理员登录</t>
+          <t>US-I-001 发送文字、表情、图片和位置共享私聊消息</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>20046</v>
       </c>
       <c r="D55" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4783,14 +4918,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 使用独立账号登录 Web 管理后台
-以便于 安全地执行平台运营与治理操作</t>
+          <t>作为 互为好友的用户
+我想要 发送文字、表情、图片和位置共享私聊消息
+以便于 在活动前后便捷沟通协调
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>US-ADM-001</t>
+          <t>US-I-001 P1 实践后延期</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4800,17 +4938,17 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4822,33 +4960,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>US-ADM-002 活动人工审核</t>
+          <t>US-I-002 在小队群聊中收发文字、表情、图片和位置共享消息</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>20047</v>
       </c>
       <c r="D56" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>迭代1-MVP核心链路</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>关键</t>
+          <t>重要</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4858,14 +4996,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 审核 AI 转人工或高风险的活动（通过/驳回/要求修改）
-以便于 保障平台活动内容合规并降低违规风险</t>
+          <t>作为 小队成员
+我想要 在小队群聊中收发文字、表情、图片和位置共享消息
+以便于 及时同步队内信息和活动安排
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>US-ADM-002</t>
+          <t>US-I-002 P1 实践后延期</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4875,17 +5016,17 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.1</t>
+          <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
@@ -4897,23 +5038,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>US-ADM-003 用户封禁与解封</t>
+          <t>US-I-003 查看会话列表及每个会话的未读消息数</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>20048</v>
       </c>
       <c r="D57" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4933,14 +5074,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 查询、封禁和解封用户并记录操作原因
-以便于 维护平台秩序并约束违规用户行为</t>
+          <t>作为 IM 用户
+我想要 查看会话列表及每个会话的未读消息数
+以便于 快速定位需要回复的对话
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>US-ADM-003</t>
+          <t>US-I-003 P1 实践后延期</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4950,12 +5094,12 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -4972,23 +5116,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>US-ADM-004 商家申请审核</t>
+          <t>US-I-004 在离线后重新上线时拉取历史消息与未读消息</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>20049</v>
       </c>
       <c r="D58" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代2-第二次迭代</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5008,14 +5152,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 审核商家入驻申请（通过/驳回并附原因）
-以便于 控制商家准入质量并保障平台商业生态</t>
+          <t>作为 IM 用户
+我想要 在离线后重新上线时拉取历史消息与未读消息
+以便于 不遗漏任何重要信息
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>US-ADM-004</t>
+          <t>US-I-004 P1 实践后延期</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5025,12 +5172,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5047,33 +5194,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>US-ADM-005 活动下架与恢复</t>
+          <t>US-I-005 在发送后 2 分钟内撤回本人消息</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>20050</v>
       </c>
       <c r="D59" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代4-后续增强</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5083,14 +5230,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 下架违规活动或在整改后恢复活动
-以便于 及时处置风险内容并减少对正常用户的影响</t>
+          <t>作为 消息发送者
+我想要 在发送后 2 分钟内撤回本人消息
+以便于 及时纠正误发内容
+优先级：P2
+目标版本：v1.1
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>US-ADM-005</t>
+          <t>US-I-005 P2 实践后延期</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5100,17 +5250,17 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v1.1</t>
         </is>
       </c>
     </row>
@@ -5122,33 +5272,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>US-ADM-006 小队停用与恢复</t>
+          <t>US-I-006 将消息转发给其他好友或小队群聊</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>20051</v>
       </c>
       <c r="D60" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>迭代2-完整功能</t>
+          <t>迭代4-后续增强</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>OnlyFriends/后台管理</t>
+          <t>OnlyFriends/即时通讯</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5158,14 +5308,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>作为 平台管理员
-我想要 停用违规小队或在整改后恢复小队
-以便于 治理社群风险并维护健康的社区环境</t>
+          <t>作为 IM 用户
+我想要 将消息转发给其他好友或小队群聊
+以便于 高效传递信息而无需重复输入
+优先级：P2
+目标版本：v1.1
+10天处理策略：实践后延期</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>US-ADM-006</t>
+          <t>US-I-006 P2 实践后延期</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5175,17 +5328,17 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>OnlyFriends_v0.5</t>
+          <t>OnlyFriends_v1.1</t>
         </is>
       </c>
     </row>
@@ -5197,293 +5350,1553 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>US-ADM-007 操作日志审计</t>
+          <t>US-I-007 看到消息未读或已读状态</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>20052</v>
       </c>
       <c r="D61" t="n">
+        <v>10004</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>OnlyFriends/即时通讯</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>作为 消息发送者
+我想要 看到消息未读或已读状态
+以便于 判断对方是否已查看重要信息
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>US-I-007 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>US-I-008 在群聊中 @ 指定成员并接收被 @ 提醒</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>20053</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10004</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>OnlyFriends/即时通讯</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>作为 小队成员
+我想要 在群聊中 @ 指定成员并接收被 @ 提醒
+以便于 确保关键信息被相关成员看到
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>US-I-008 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>US-AI-001 对用户提交的活动内容执行规则引擎、LLM 和人工兜底的安全审核</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>20054</v>
+      </c>
+      <c r="D63" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>OnlyFriends/AI服务</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>关键</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>作为 平台运营方
+我想要 对用户提交的活动内容执行规则引擎、LLM 和人工兜底的安全审核
+以便于 在审核效率与内容合规之间取得平衡
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>US-AI-001 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>US-AI-002 输入主题后获得 AI 生成的活动策划方案，并支持逐项修改</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>20055</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>OnlyFriends/AI服务</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>作为 活动发起人
+我想要 输入主题后获得 AI 生成的活动策划方案，并支持逐项修改
+以便于 快速完成活动设计并减少策划时间
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>US-AI-002 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>US-AI-003 在发布活动总结时由 AI 自动分类图片，并由我人工确认分类结果</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>20056</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>OnlyFriends/AI服务</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>作为 活动发起人
+我想要 在发布活动总结时由 AI 自动分类图片，并由我人工确认分类结果
+以便于 高效整理活动素材并保证总结内容准确
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>US-AI-003 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>US-ADM-001 使用系统预先创建的独立账号登录 Web 管理后台</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>20057</v>
+      </c>
+      <c r="D66" t="n">
         <v>10006</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>迭代3-体验增强</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>OnlyFriends/后台管理</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>关键</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 使用系统预先创建的独立账号登录 Web 管理后台
+以便于 安全地执行平台运营与治理操作
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>US-ADM-001 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>US-ADM-002 审核 AI 转人工或高风险活动，并给出通过、驳回或要求修改结果</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>20058</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>迭代1-首次迭代MVP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>关键</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 审核 AI 转人工或高风险活动，并给出通过、驳回或要求修改结果
+以便于 保障活动内容合规并降低违规风险
+优先级：P0
+目标版本：v0.1
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>US-ADM-002 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>US-ADM-003 封禁和解封用户，并在封禁时填写原因和期限</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>20059</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 封禁和解封用户，并在封禁时填写原因和期限
+以便于 维护平台秩序并约束违规用户行为
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>US-ADM-003 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>US-ADM-004 审核商家入驻申请，并在驳回时填写原因</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>20060</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 审核商家入驻申请，并在驳回时填写原因
+以便于 控制商家准入质量并保障平台商业生态
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>US-ADM-004 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>US-ADM-005 下架违规活动或在整改后恢复活动，并记录处理原因</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>20061</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 下架违规活动或在整改后恢复活动，并记录处理原因
+以便于 及时处置风险内容并减少对正常用户的影响
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>US-ADM-005 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>US-ADM-006 停用违规小队或在整改后恢复小队，并记录停用原因</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>20062</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 停用违规小队或在整改后恢复小队，并记录停用原因
+以便于 治理社群风险并维护健康社区环境
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>US-ADM-006 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>US-ADM-007 查看管理员操作日志</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>20063</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>迭代4-后续增强</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>作为 平台管理员
 我想要 查看管理员操作日志
-以便于 满足审计要求并追溯历史治理操作</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>US-ADM-007</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+以便于 满足审计要求并追溯历史治理操作
+优先级：P2
+目标版本：v1.1
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>US-ADM-007 P2 实践后延期</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>OnlyFriends_v1.1</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>US-N-001 接收与管理系统通知</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>20053</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>US-ADM-008 修改本人登录密码</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>20064</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 修改本人登录密码
+以便于 提升后台账号安全性
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>US-ADM-008 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>US-ADM-009 查询个人用户和商家用户，并查看账号状态、发布活动和创建小队</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>20065</v>
+      </c>
+      <c r="D74" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 查询个人用户和商家用户，并查看账号状态、发布活动和创建小队
+以便于 了解用户行为并辅助治理决策
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>US-ADM-009 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>US-ADM-010 查询全部活动并按活动状态筛选</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20066</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 查询全部活动并按活动状态筛选
+以便于 快速定位需要审核或治理的活动
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>US-ADM-010 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>US-ADM-011 查询全部小队并查看成员、队内活动和举报记录</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>20067</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10006</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>OnlyFriends/后台管理</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>作为 平台管理员
+我想要 查询全部小队并查看成员、队内活动和举报记录
+以便于 识别违规社群并进行治理
+优先级：P1
+目标版本：v0.5
+10天处理策略：实践后延期</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>US-ADM-011 P1 实践后延期</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>US-N-001 接收活动审核结果、等待队列递补和报名结果等系统通知</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>20068</v>
+      </c>
+      <c r="D77" t="n">
         <v>10007</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>迭代2-完整功能</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>OnlyFriends/通知模块</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>重要</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>作为 个人用户
-我想要 接收系统通知（审核结果、等待队列递补等）并标记已读
-以便于 及时处理待办事项而不遗漏重要信息</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>US-N-001</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+我想要 接收活动审核结果、等待队列递补和报名结果等系统通知
+以便于 及时处理待办事项而不遗漏重要信息
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>US-N-001 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.5</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>US-INF-001 API网关统一管控</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>20054</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>US-N-002 查看通知列表并将通知标记为已读</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>20069</v>
+      </c>
+      <c r="D78" t="n">
+        <v>10007</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>迭代2-第二次迭代</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>OnlyFriends/通知模块</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>作为 个人用户
+我想要 查看通知列表并将通知标记为已读
+以便于 管理自己的系统消息和未读状态
+优先级：P1
+目标版本：v0.5
+10天处理策略：第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>US-N-002 P1 第二次迭代择优</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>OnlyFriends_v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>US-INF-001 通过 API 网关实现统一路由、鉴权和基础限流</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>20070</v>
+      </c>
+      <c r="D79" t="n">
         <v>10008</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>迭代0-基础设施</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>迭代0-启动与规划</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>OnlyFriends/基础设施</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>关键</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>作为 开发/运维人员
-我想要 通过 API 网关实现统一路由、鉴权和限流
-以便于 保障平台服务的安全性与稳定性</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>US-INF-001</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+我想要 通过 API 网关实现统一路由、鉴权和基础限流
+以便于 保障平台服务的安全性与稳定性
+优先级：P0
+目标版本：v0.0
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>US-INF-001 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.0</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>story</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>US-INF-002 微服务契约化通信</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>20055</v>
-      </c>
-      <c r="D64" t="n">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>US-INF-002 各微服务通过契约化接口通信并遵循服务边界</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>20071</v>
+      </c>
+      <c r="D80" t="n">
         <v>10008</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>迭代0-基础设施</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>迭代0-启动与规划</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>OnlyFriends/基础设施</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>关键</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>作为 开发团队成员
-我想要 各微服务通过 OpenFeign 契约通信并遵循逻辑分库原则
-以便于 团队并行开发并清晰控制服务边界</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>US-INF-002</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
+我想要 各微服务通过契约化接口通信并遵循服务边界
+以便于 团队并行开发并降低联调风险
+优先级：P0
+目标版本：v0.0
+10天处理策略：第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>US-INF-002 P0 第一次迭代必做</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>OnlyFriends_v0.0</t>
         </is>
